--- a/client/public/booking-template-with-readme-1.xlsx
+++ b/client/public/booking-template-with-readme-1.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Number of consecutive monthly assistance rounds this booking covers. Must be exactly 1 or 3 — no other value is accepted. Rounds 1 covers one calendar month starting from Start Date; Rounds 3 covers three consecutive calendar months. The value also determines the required End Date, which equals Start Date + Rounds calendar months (see End Date row).</t>
+          <t>Number of consecutive monthly assistance rounds this booking covers. Must be 1, 2 or 3 — no other value is accepted. Rounds 1 covers one calendar month starting from Start Date; Rounds 2 covers two consecutive calendar months; Rounds 3 covers three consecutive calendar months. The value also determines the required End Date, which equals Start Date + Rounds calendar months (see End Date row).</t>
         </is>
       </c>
     </row>
